--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC86D772-04A6-4959-AE39-9957EDA2266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5385" yWindow="2685" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6405" yWindow="1905" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techniques" sheetId="36" r:id="rId1"/>

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC86D772-04A6-4959-AE39-9957EDA2266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E90B2C-99E8-4CAE-B964-0AF27D57E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6405" yWindow="1905" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techniques" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="176">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -681,62 +681,6 @@
   <si>
     <t>needTech</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>37</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>39</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>测试5</t>
-  </si>
-  <si>
-    <t>测试6</t>
-  </si>
-  <si>
-    <t>测试7</t>
-  </si>
-  <si>
-    <t>测试8</t>
   </si>
 </sst>
 </file>
@@ -3398,54 +3342,20 @@
     </row>
     <row r="41" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3"/>
-      <c r="B41" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="4">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M41" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N41" s="4">
-        <v>4</v>
-      </c>
-      <c r="O41" s="4">
-        <v>1</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R41" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="R41" s="16"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
@@ -3453,54 +3363,20 @@
     </row>
     <row r="42" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3"/>
-      <c r="B42" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="4">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="4">
-        <v>2</v>
-      </c>
-      <c r="H42" s="4">
-        <v>1</v>
-      </c>
-      <c r="I42" s="4">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M42" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N42" s="4">
-        <v>4</v>
-      </c>
-      <c r="O42" s="4">
-        <v>1</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R42" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="R42" s="16"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
@@ -3508,54 +3384,20 @@
     </row>
     <row r="43" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3"/>
-      <c r="B43" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="4">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="4">
-        <v>3</v>
-      </c>
-      <c r="H43" s="4">
-        <v>1</v>
-      </c>
-      <c r="I43" s="4">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4">
-        <v>0</v>
-      </c>
-      <c r="K43" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M43" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N43" s="4">
-        <v>4</v>
-      </c>
-      <c r="O43" s="4">
-        <v>1</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R43" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="R43" s="16"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
@@ -3563,54 +3405,20 @@
     </row>
     <row r="44" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3"/>
-      <c r="B44" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="4">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="4">
-        <v>3</v>
-      </c>
-      <c r="H44" s="4">
-        <v>1</v>
-      </c>
-      <c r="I44" s="4">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M44" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N44" s="4">
-        <v>4</v>
-      </c>
-      <c r="O44" s="4">
-        <v>1</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R44" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="R44" s="16"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
@@ -3618,54 +3426,20 @@
     </row>
     <row r="45" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3"/>
-      <c r="B45" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="4">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="4">
-        <v>3</v>
-      </c>
-      <c r="H45" s="4">
-        <v>1</v>
-      </c>
-      <c r="I45" s="4">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M45" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N45" s="4">
-        <v>4</v>
-      </c>
-      <c r="O45" s="4">
-        <v>2</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="R45" s="16"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
@@ -3673,54 +3447,20 @@
     </row>
     <row r="46" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3"/>
-      <c r="B46" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="4">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="4">
-        <v>3</v>
-      </c>
-      <c r="H46" s="4">
-        <v>1</v>
-      </c>
-      <c r="I46" s="4">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M46" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N46" s="4">
-        <v>4</v>
-      </c>
-      <c r="O46" s="4">
-        <v>2</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R46" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="R46" s="16"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
@@ -3728,54 +3468,20 @@
     </row>
     <row r="47" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3"/>
-      <c r="B47" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="4">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="4">
-        <v>3</v>
-      </c>
-      <c r="H47" s="4">
-        <v>1</v>
-      </c>
-      <c r="I47" s="4">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M47" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N47" s="4">
-        <v>4</v>
-      </c>
-      <c r="O47" s="4">
-        <v>3</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R47" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="R47" s="16"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
@@ -3783,54 +3489,20 @@
     </row>
     <row r="48" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3"/>
-      <c r="B48" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="4">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="4">
-        <v>3</v>
-      </c>
-      <c r="H48" s="4">
-        <v>1</v>
-      </c>
-      <c r="I48" s="4">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M48" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N48" s="4">
-        <v>4</v>
-      </c>
-      <c r="O48" s="4">
-        <v>3</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R48" s="16" t="s">
-        <v>127</v>
-      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="R48" s="16"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E90B2C-99E8-4CAE-B964-0AF27D57E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCFD21-6BA8-4852-B86B-227D611A6186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCFD21-6BA8-4852-B86B-227D611A6186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234B313D-2313-4A17-88EE-4F757482A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techniques" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="179">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -643,32 +643,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopChangeTroops",value:10,kinds:[2]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:10,kinds:[3]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:15,kinds:[2]},{class:"TroopAddAttack",value:10,kinds:[2]},{class:"TroopAddDefence",value:10,kinds:[2]},{class:"TroopAddMoveAbility",value:6,kinds:[2]}]</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:15,kinds:[3]},{class:"TroopAddAttack",value:10,kinds:[3]},{class:"TroopAddDefence",value:10,kinds:[3]},{class:"TroopAddMoveAbility",value:6,kinds:[3]}]</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:10,kinds:[4]}]</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:15,kinds:[4]},{class:"TroopAddAttack",value:10,kinds:[4]},{class:"TroopAddDefence",value:10,kinds:[4]},{class:"TroopAddMoveAbility",value:6,kinds:[4]}]</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:10,kinds:[5]}]</t>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeTroops",value:15,kinds:[5]},{class:"TroopAddAttack",value:10,kinds:[5]},{class:"TroopAddDefence",value:10,kinds:[5]},{class:"TroopAddMoveAbility",value:6,kinds:[5]}]</t>
-  </si>
-  <si>
     <t>[{class:"ForceCityMaxMorale", value:20}]</t>
   </si>
   <si>
@@ -680,6 +654,50 @@
   </si>
   <si>
     <t>needTech</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility",value:10,kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:10,kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:10,kinds:[2]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:10,kinds:[3]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:10,kinds:[4]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:2, condition:{class:"andList",list:[{class:"SkillIdInList", ids:[22], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:15,kinds:[2]},{class:"TroopAddAttack",value:10,kinds:[2]},{class:"TroopAddDefence",value:10,kinds:[2]},{class:"TroopAddMoveAbility",value:6,kinds:[2]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:15,kinds:[3]},{class:"TroopAddAttack",value:10,kinds:[3]},{class:"TroopAddDefence",value:10,kinds:[3]},{class:"TroopAddMoveAbility",value:6,kinds:[3]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:15,kinds:[4]},{class:"TroopAddAttack",value:10,kinds:[4]},{class:"TroopAddDefence",value:10,kinds:[4]},{class:"TroopAddMoveAbility",value:6,kinds:[4]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage",value:15,kinds:[5]},{class:"TroopAddAttack",value:10,kinds:[5]},{class:"TroopAddDefence",value:10,kinds:[5]},{class:"TroopAddMoveAbility",value:6,kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:1,isRange:1,kinds:[4]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +705,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,6 +748,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -804,7 +830,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -857,10 +883,24 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1189,7 +1229,7 @@
     <col min="14" max="14" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="103.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="103.75" style="23" customWidth="1"/>
     <col min="18" max="18" width="66" style="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
@@ -1237,7 +1277,7 @@
         <v>101</v>
       </c>
       <c r="P1" s="13"/>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="19" t="s">
         <v>102</v>
       </c>
       <c r="R1" s="6"/>
@@ -1268,7 +1308,7 @@
       <c r="N2"/>
       <c r="O2"/>
       <c r="P2"/>
-      <c r="Q2" s="19"/>
+      <c r="Q2" s="20"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1318,10 +1358,10 @@
         <v>92</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="P3" s="7"/>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="21" t="s">
         <v>94</v>
       </c>
       <c r="R3" s="15"/>
@@ -1382,7 +1422,7 @@
       <c r="P4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="Q4" s="22" t="s">
         <v>104</v>
       </c>
       <c r="R4" s="17" t="s">
@@ -1431,8 +1471,8 @@
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
-      <c r="Q5" s="2" t="s">
-        <v>164</v>
+      <c r="Q5" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="R5" s="16" t="s">
         <v>126</v>
@@ -1597,8 +1637,8 @@
       <c r="P8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>166</v>
+      <c r="Q8" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R8" s="16" t="s">
         <v>129</v>
@@ -1650,8 +1690,8 @@
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="2" t="s">
-        <v>165</v>
+      <c r="Q9" s="23" t="s">
+        <v>171</v>
       </c>
       <c r="R9" s="16" t="s">
         <v>130</v>
@@ -1815,8 +1855,8 @@
       <c r="P12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>167</v>
+      <c r="Q12" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="R12" s="16" t="s">
         <v>133</v>
@@ -1868,8 +1908,8 @@
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="2" t="s">
-        <v>168</v>
+      <c r="Q13" s="23" t="s">
+        <v>172</v>
       </c>
       <c r="R13" s="16" t="s">
         <v>134</v>
@@ -1979,6 +2019,9 @@
       <c r="P15" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="Q15" s="18" t="s">
+        <v>178</v>
+      </c>
       <c r="R15" s="16" t="s">
         <v>136</v>
       </c>
@@ -2033,8 +2076,8 @@
       <c r="P16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>169</v>
+      <c r="Q16" s="23" t="s">
+        <v>176</v>
       </c>
       <c r="R16" s="16" t="s">
         <v>137</v>
@@ -2086,8 +2129,8 @@
       </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="2" t="s">
-        <v>170</v>
+      <c r="Q17" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="R17" s="16" t="s">
         <v>138</v>
@@ -2143,6 +2186,9 @@
       <c r="P18" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="Q18" s="23" t="s">
+        <v>168</v>
+      </c>
       <c r="R18" s="16" t="s">
         <v>139</v>
       </c>
@@ -2251,8 +2297,8 @@
       <c r="P20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>171</v>
+      <c r="Q20" s="23" t="s">
+        <v>177</v>
       </c>
       <c r="R20" s="16" t="s">
         <v>141</v>
@@ -2304,8 +2350,8 @@
       </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
-      <c r="Q21" s="2" t="s">
-        <v>172</v>
+      <c r="Q21" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="R21" s="16" t="s">
         <v>142</v>
@@ -2415,8 +2461,8 @@
       <c r="P23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>173</v>
+      <c r="Q23" s="23" t="s">
+        <v>165</v>
       </c>
       <c r="R23" s="16" t="s">
         <v>144</v>
@@ -2522,7 +2568,7 @@
       </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
-      <c r="Q25" s="2" t="s">
+      <c r="Q25" s="23" t="s">
         <v>147</v>
       </c>
       <c r="R25" s="16" t="s">
@@ -2845,7 +2891,7 @@
       <c r="P31" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="Q31" s="23" t="s">
         <v>124</v>
       </c>
       <c r="R31" s="16" t="s">
@@ -2902,8 +2948,8 @@
       <c r="P32" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="Q32" s="2" t="s">
-        <v>174</v>
+      <c r="Q32" s="23" t="s">
+        <v>166</v>
       </c>
       <c r="R32" s="16" t="s">
         <v>154</v>
@@ -3009,6 +3055,9 @@
       <c r="P34" s="4" t="s">
         <v>69</v>
       </c>
+      <c r="Q34" s="18" t="s">
+        <v>173</v>
+      </c>
       <c r="R34" s="16" t="s">
         <v>156</v>
       </c>
@@ -3167,7 +3216,7 @@
       </c>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
-      <c r="Q37" s="2" t="s">
+      <c r="Q37" s="23" t="s">
         <v>125</v>
       </c>
       <c r="R37" s="16" t="s">

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234B313D-2313-4A17-88EE-4F757482A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52D36BA-CDD2-4A76-9F41-DA8CE7700589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="180">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -699,6 +699,9 @@
   <si>
     <t>[{class:"TroopChangeSkillSpellRange", value:1,isRange:1,kinds:[4]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddSkill", value:2,  kinds:[5]}]</t>
   </si>
 </sst>
 </file>
@@ -2243,6 +2246,9 @@
       <c r="P19" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="Q19" s="23" t="s">
+        <v>179</v>
+      </c>
       <c r="R19" s="16" t="s">
         <v>140</v>
       </c>

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52D36BA-CDD2-4A76-9F41-DA8CE7700589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80F0D20-AE0C-4471-92BB-DBE9AB1B1B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="181">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -702,6 +702,23 @@
   </si>
   <si>
     <t>[{class:"TroopAddSkill", value:2,  kinds:[5]}]</t>
+  </si>
+  <si>
+    <t>[
+        {
+          "class": "TroopChangeSkillAttackRange",
+          "atkType": 5,
+          "atkRange": 1,
+          "conditon": {
+            "class": "SkillIdInList",
+            "ids": [
+              18
+            ],
+            "result": 1
+          }
+        }
+      ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -833,7 +850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -903,6 +920,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2693,7 +2713,7 @@
       <c r="V27" s="4"/>
       <c r="X27" s="4"/>
     </row>
-    <row r="28" spans="2:24" ht="54" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:24" ht="189" x14ac:dyDescent="0.15">
       <c r="B28" s="2">
         <v>24</v>
       </c>
@@ -2738,6 +2758,9 @@
       </c>
       <c r="P28" s="4" t="s">
         <v>56</v>
+      </c>
+      <c r="Q28" s="24" t="s">
+        <v>180</v>
       </c>
       <c r="R28" s="16" t="s">
         <v>150</v>

--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80F0D20-AE0C-4471-92BB-DBE9AB1B1B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B58A0ED-2303-4D0B-8447-766E620D94B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techniques" sheetId="36" r:id="rId1"/>
@@ -1235,29 +1235,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:Y68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.36328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="103.75" style="23" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="103.7265625" style="23" customWidth="1"/>
     <col min="18" max="18" width="66" style="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1312,7 +1312,7 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1340,7 +1340,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
     </row>
-    <row r="3" spans="1:25" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1396,7 +1396,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
     </row>
-    <row r="4" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="V5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1560,7 +1560,7 @@
       <c r="V6" s="4"/>
       <c r="X6" s="4"/>
     </row>
-    <row r="7" spans="1:25" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" ht="42" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -1614,7 +1614,7 @@
       <c r="V7" s="4"/>
       <c r="X7" s="4"/>
     </row>
-    <row r="8" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:25" ht="28" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -1671,7 +1671,7 @@
       <c r="V8" s="4"/>
       <c r="X8" s="4"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="V9" s="4"/>
       <c r="X9" s="4"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -1778,7 +1778,7 @@
       <c r="V10" s="4"/>
       <c r="X10" s="4"/>
     </row>
-    <row r="11" spans="1:25" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:25" ht="56" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="V11" s="4"/>
       <c r="X11" s="4"/>
     </row>
-    <row r="12" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:25" ht="28" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -1889,7 +1889,7 @@
       <c r="V12" s="4"/>
       <c r="X12" s="4"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -1942,7 +1942,7 @@
       <c r="V13" s="4"/>
       <c r="X13" s="4"/>
     </row>
-    <row r="14" spans="1:25" ht="54" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:25" ht="56" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="V14" s="4"/>
       <c r="X14" s="4"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -2053,7 +2053,7 @@
       <c r="V15" s="4"/>
       <c r="X15" s="4"/>
     </row>
-    <row r="16" spans="1:25" ht="27" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:25" ht="28" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>12</v>
       </c>
@@ -2110,7 +2110,7 @@
       <c r="V16" s="4"/>
       <c r="X16" s="4"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -2163,7 +2163,7 @@
       <c r="V17" s="4"/>
       <c r="X17" s="4"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="V18" s="4"/>
       <c r="X18" s="4"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="V19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="2:24" ht="27" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="V20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <v>17</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="V21" s="4"/>
       <c r="X21" s="4"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="V22" s="4"/>
       <c r="X22" s="4"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="V23" s="4"/>
       <c r="X23" s="4"/>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -2552,7 +2552,7 @@
       <c r="V24" s="4"/>
       <c r="X24" s="4"/>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2">
         <v>21</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="V25" s="4"/>
       <c r="X25" s="4"/>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>22</v>
       </c>
@@ -2659,7 +2659,7 @@
       <c r="V26" s="4"/>
       <c r="X26" s="4"/>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>23</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="V27" s="4"/>
       <c r="X27" s="4"/>
     </row>
-    <row r="28" spans="2:24" ht="189" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:24" ht="196" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>24</v>
       </c>
@@ -2770,7 +2770,7 @@
       <c r="V28" s="4"/>
       <c r="X28" s="4"/>
     </row>
-    <row r="29" spans="2:24" ht="27" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>25</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="V29" s="4"/>
       <c r="X29" s="4"/>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <v>26</v>
       </c>
@@ -2874,7 +2874,7 @@
       <c r="V30" s="4"/>
       <c r="X30" s="4"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <v>27</v>
       </c>
@@ -2931,7 +2931,7 @@
       <c r="V31" s="4"/>
       <c r="X31" s="4"/>
     </row>
-    <row r="32" spans="2:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <v>28</v>
       </c>
@@ -2988,7 +2988,7 @@
       <c r="V32" s="4"/>
       <c r="X32" s="4"/>
     </row>
-    <row r="33" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <v>29</v>
       </c>
@@ -3038,7 +3038,7 @@
       <c r="V33" s="4"/>
       <c r="X33" s="4"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>30</v>
       </c>
@@ -3095,7 +3095,7 @@
       <c r="V34" s="4"/>
       <c r="X34" s="4"/>
     </row>
-    <row r="35" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>31</v>
       </c>
@@ -3149,7 +3149,7 @@
       <c r="V35" s="4"/>
       <c r="X35" s="4"/>
     </row>
-    <row r="36" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
         <v>32</v>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="V36" s="4"/>
       <c r="X36" s="4"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B37" s="2">
         <v>33</v>
       </c>
@@ -3256,7 +3256,7 @@
       <c r="V37" s="4"/>
       <c r="X37" s="4"/>
     </row>
-    <row r="38" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
         <v>34</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="V38" s="4"/>
       <c r="X38" s="4"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>35</v>
       </c>
@@ -3364,7 +3364,7 @@
       <c r="V39" s="4"/>
       <c r="X39" s="4"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>36</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="V40" s="4"/>
       <c r="X40" s="4"/>
     </row>
-    <row r="41" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3439,7 +3439,7 @@
       <c r="V41" s="4"/>
       <c r="X41" s="4"/>
     </row>
-    <row r="42" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3460,7 +3460,7 @@
       <c r="V42" s="4"/>
       <c r="X42" s="4"/>
     </row>
-    <row r="43" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3481,7 +3481,7 @@
       <c r="V43" s="4"/>
       <c r="X43" s="4"/>
     </row>
-    <row r="44" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3502,7 +3502,7 @@
       <c r="V44" s="4"/>
       <c r="X44" s="4"/>
     </row>
-    <row r="45" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3523,7 +3523,7 @@
       <c r="V45" s="4"/>
       <c r="X45" s="4"/>
     </row>
-    <row r="46" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3544,7 +3544,7 @@
       <c r="V46" s="4"/>
       <c r="X46" s="4"/>
     </row>
-    <row r="47" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -3565,7 +3565,7 @@
       <c r="V47" s="4"/>
       <c r="X47" s="4"/>
     </row>
-    <row r="48" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -3586,140 +3586,140 @@
       <c r="V48" s="4"/>
       <c r="X48" s="4"/>
     </row>
-    <row r="49" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
     </row>
-    <row r="50" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
     </row>
-    <row r="51" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
     </row>
-    <row r="52" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
     </row>
-    <row r="53" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
     </row>
-    <row r="56" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
       <c r="P56" s="4"/>
     </row>
-    <row r="57" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
       <c r="P57" s="4"/>
     </row>
-    <row r="58" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
     </row>
-    <row r="59" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
       <c r="P59" s="4"/>
     </row>
-    <row r="60" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
       <c r="P61" s="4"/>
     </row>
-    <row r="62" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
       <c r="P62" s="4"/>
     </row>
-    <row r="63" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
       <c r="P63" s="4"/>
     </row>
-    <row r="64" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4"/>
     </row>
-    <row r="65" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4"/>
     </row>
-    <row r="66" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
       <c r="P66" s="4"/>
     </row>
-    <row r="67" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
       <c r="P67" s="4"/>
     </row>
-    <row r="68" spans="4:16" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="N68" s="4"/>
